--- a/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_generator_bearings_clustering/clustering/dsas_g11_generator_bearings/clustering_g11_generator_bearings_output2.xlsx
+++ b/Techniques/AI Driven Machine Learning and Clustering/outputs/G11/dsas_g11_generator_bearings_clustering/clustering/dsas_g11_generator_bearings/clustering_g11_generator_bearings_output2.xlsx
@@ -656,7 +656,7 @@
         <v>40</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.705157585327195</v>
+        <v>1.741485279826332</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.767362283106212</v>
+        <v>1.802901449708824</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>40</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.819530135065987</v>
+        <v>1.854698352259124</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>40</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.857158018185761</v>
+        <v>1.890960990496432</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>40</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.862282293510545</v>
+        <v>1.895273390626914</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>40</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.881567302245708</v>
+        <v>1.914601694528801</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>40</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.87701503124468</v>
+        <v>1.909473623738011</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.783558598908552</v>
+        <v>1.816783587340624</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.871158813097629</v>
+        <v>1.903038714235977</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>40</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.923194246083626</v>
+        <v>1.951128932033638</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.964917364107344</v>
+        <v>1.99125691220827</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>40</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.959753681397427</v>
+        <v>1.985507979050622</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>40</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.979144366385507</v>
+        <v>2.004102854537665</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.959932496779369</v>
+        <v>1.987280953239381</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>40</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.022281408194178</v>
+        <v>2.052257507955008</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.988187278992141</v>
+        <v>2.013125875356126</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.01145949646771</v>
+        <v>2.035573186447783</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>40</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.037137536945347</v>
+        <v>2.060417431895696</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>40</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.898400121264403</v>
+        <v>1.921557489802123</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.869957927880978</v>
+        <v>1.89416406865179</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>40</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.947148301083497</v>
+        <v>1.977234811848232</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>40</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.010440578025532</v>
+        <v>2.036298539020042</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>40</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.944689360919299</v>
+        <v>1.971048170772894</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>40</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.914916671267877</v>
+        <v>1.941391564614081</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>40</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.796963422559948</v>
+        <v>1.824431617609811</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.708589733238733</v>
+        <v>1.736549940087732</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>40</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.637791187931315</v>
+        <v>1.662071111947776</v>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>40</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87995331999446</v>
+        <v>1.893633881734282</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.865307983401752</v>
+        <v>1.878128865053979</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>40</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.732407038736812</v>
+        <v>1.745111032382458</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.570217252286406</v>
+        <v>1.583183184920332</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>40</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.354899153208561</v>
+        <v>1.3803836129005</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>40</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.257147014116125</v>
+        <v>1.281063025656791</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>40</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.549953717458954</v>
+        <v>1.558862782957788</v>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>40</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.623363433560709</v>
+        <v>1.631475010287043</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>40</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.71014210691728</v>
+        <v>1.717442539068047</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>40</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.702426203120455</v>
+        <v>1.709207783271603</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>40</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.48870384990903</v>
+        <v>1.509635922043287</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>40</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.59379871357722</v>
+        <v>1.619820859522152</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -4166,7 +4166,7 @@
         <v>40</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.641350795987709</v>
+        <v>1.661440413655807</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>40</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.595471988009198</v>
+        <v>1.615480808086495</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>40</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.550879801674148</v>
+        <v>1.570786777430053</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>40</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.462899365061929</v>
+        <v>1.483536870122164</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>40</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.328391905435018</v>
+        <v>1.356501232000801</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         <v>40</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.421089512074382</v>
+        <v>1.454001390910001</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>40</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.520954991528347</v>
+        <v>1.553060865087595</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>40</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.552545223291381</v>
+        <v>1.585209643034718</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>40</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.540775609669771</v>
+        <v>1.572511283318393</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>40</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.466393401512167</v>
+        <v>1.498746520587712</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>40</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.481705970815983</v>
+        <v>1.514177266504126</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>40</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.464318065220977</v>
+        <v>1.492514786344906</v>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>40</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.409014180931551</v>
+        <v>1.430280435534318</v>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>40</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.369203904512999</v>
+        <v>1.384997265712242</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>40</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.347330422934502</v>
+        <v>1.363294812401204</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>40</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.243986342366167</v>
+        <v>1.258965455845251</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>40</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.253509502712617</v>
+        <v>1.274518850255723</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>40</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.336779916180173</v>
+        <v>1.355013103123816</v>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>40</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.528910266531682</v>
+        <v>1.54266765228096</v>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>40</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.560347780111084</v>
+        <v>1.573521989850639</v>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>40</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.584700573081944</v>
+        <v>1.597380281174255</v>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>40</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.601275008124682</v>
+        <v>1.613554156644161</v>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         <v>40</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.637172307507579</v>
+        <v>1.646696382812853</v>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>40</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.758559545544131</v>
+        <v>1.762694881440977</v>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>40</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.718882305933196</v>
+        <v>1.722228007419979</v>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>40</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.694384964067655</v>
+        <v>1.697025106578216</v>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>40</v>
       </c>
       <c r="AA67" t="n">
-        <v>1.557652750658715</v>
+        <v>1.558923033951106</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>40</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.309723886194334</v>
+        <v>1.32438881280846</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>40</v>
       </c>
       <c r="AA69" t="n">
-        <v>1.260452611274063</v>
+        <v>1.283741372860274</v>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>40</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.378667270733263</v>
+        <v>1.39442465465971</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>40</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.451678330634119</v>
+        <v>1.467548653183033</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>40</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.527816674212019</v>
+        <v>1.54323981943776</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>40</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.385749209623677</v>
+        <v>1.401375294891445</v>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>40</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.391020551670312</v>
+        <v>1.414850704233075</v>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>90</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.2086383788729263</v>
+        <v>0.2482070822969333</v>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         <v>90</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.1872901352021601</v>
+        <v>0.2238402623206531</v>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         <v>90</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.1279004444466521</v>
+        <v>0.1881776826437973</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>90</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.159117888037337</v>
+        <v>0.2172414940367761</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>90</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.1979056275685695</v>
+        <v>0.2620706859782232</v>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>40</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.249406465509918</v>
+        <v>1.270694493625046</v>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>40</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.355643645500663</v>
+        <v>1.379287057563778</v>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>40</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.356918768804563</v>
+        <v>1.380124041287635</v>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>40</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.367475177582943</v>
+        <v>1.390438881850593</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>40</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.370634710535268</v>
+        <v>1.394895685912896</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>40</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.270420857765605</v>
+        <v>1.296719900098682</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>40</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.267045541137621</v>
+        <v>1.29691574487005</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         <v>40</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.524641777276031</v>
+        <v>1.553591371262951</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>40</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.50649883657372</v>
+        <v>1.5312203335425</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>40</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.542855154337837</v>
+        <v>1.565711229965163</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>40</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.587184713046455</v>
+        <v>1.608133132357057</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>40</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.539889537249461</v>
+        <v>1.559873736112535</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         <v>40</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.313715537277169</v>
+        <v>1.3344570913208</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>40</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.353594893405778</v>
+        <v>1.380050410512759</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>40</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.369007331263294</v>
+        <v>1.39684521475583</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>40</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.357328285194565</v>
+        <v>1.387639573734638</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>40</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.400465115470431</v>
+        <v>1.43077098818547</v>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>40</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.409147005743998</v>
+        <v>1.440091555663993</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>40</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.394966999439841</v>
+        <v>1.428033976596446</v>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>40</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.417147999943685</v>
+        <v>1.449961270914214</v>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>40</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.470826836452208</v>
+        <v>1.502212403932868</v>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>40</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.461825528812255</v>
+        <v>1.492874892402374</v>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>40</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.418280746285626</v>
+        <v>1.451649480309397</v>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>40</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.365699107826249</v>
+        <v>1.400554333995204</v>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>40</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.418832696199047</v>
+        <v>1.454212576896989</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>40</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.484646512093758</v>
+        <v>1.520279308159278</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>40</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.532816322781269</v>
+        <v>1.568254141860943</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>40</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.549179300484915</v>
+        <v>1.581834243460501</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>40</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.548102855130627</v>
+        <v>1.57847871083441</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>40</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.430631071767108</v>
+        <v>1.462253952837494</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>40</v>
       </c>
       <c r="AA110" t="n">
-        <v>1.363258203677115</v>
+        <v>1.395146077313052</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>40</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.379910873413473</v>
+        <v>1.410641367771443</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
@@ -10556,7 +10556,7 @@
         <v>40</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.45619919841659</v>
+        <v>1.486252536369086</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>40</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.525018932631162</v>
+        <v>1.552888796997355</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>40</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.573567602062342</v>
+        <v>1.598549828347881</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>40</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.589673075721286</v>
+        <v>1.612976492827601</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>40</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.479060043707023</v>
+        <v>1.505476208139044</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>40</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.356118376508097</v>
+        <v>1.381328261480385</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
@@ -11096,11 +11096,11 @@
         <v>40</v>
       </c>
       <c r="AA118" t="n">
-        <v>0.4115927613234631</v>
+        <v>1.394111806848742</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
         <v>90</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.2390950313994101</v>
+        <v>0.380381098739869</v>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>90</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.1625003966572506</v>
+        <v>0.3480639134598956</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>90</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.3570365178344849</v>
+        <v>0.278142346398098</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>90</v>
       </c>
       <c r="AA122" t="n">
-        <v>0.2522152520299246</v>
+        <v>0.2225334096601734</v>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>90</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.190132926724395</v>
+        <v>0.24639726634436</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>40</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.290702987646902</v>
+        <v>1.305493512667312</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>40</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.607704930785791</v>
+        <v>1.629706345806467</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>40</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.64893822360765</v>
+        <v>1.670264410840252</v>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>40</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.720167043330335</v>
+        <v>1.7424998226205</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         <v>40</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.753775556327429</v>
+        <v>1.78038392342651</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>40</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.85951736664198</v>
+        <v>1.886029069486873</v>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>40</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.495936449877787</v>
+        <v>1.51766754970897</v>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>40</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.435387960934417</v>
+        <v>1.457609126922093</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>40</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.38249465180493</v>
+        <v>1.403074252463152</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>40</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.497152174877359</v>
+        <v>1.503745999083743</v>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>40</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.840525183700453</v>
+        <v>1.8353648428857</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>40</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.865535816051602</v>
+        <v>1.859222557504657</v>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>40</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.93672874083756</v>
+        <v>1.929641890045757</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
@@ -12806,11 +12806,11 @@
         <v>40</v>
       </c>
       <c r="AA137" t="n">
-        <v>0.3096703535509627</v>
+        <v>2.012479206547189</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12896,7 @@
         <v>-1</v>
       </c>
       <c r="AA138" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>-1</v>
       </c>
       <c r="AA139" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>40</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.915829289726627</v>
+        <v>1.904533953371777</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>40</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.901578003320132</v>
+        <v>1.889729029985407</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>40</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.72141590698936</v>
+        <v>1.71118182071111</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>40</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.648365141556278</v>
+        <v>1.636425686990012</v>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
@@ -13436,11 +13436,11 @@
         <v>40</v>
       </c>
       <c r="AA144" t="n">
-        <v>0.3779435514320595</v>
+        <v>1.166076131715281</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -13526,11 +13526,11 @@
         <v>40</v>
       </c>
       <c r="AA145" t="n">
-        <v>0.448949342668061</v>
+        <v>1.121846424429728</v>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>Healthy (Optimal Performance)</t>
+          <t>Investigation Needed (Operational Drift)</t>
         </is>
       </c>
     </row>
@@ -13616,7 +13616,7 @@
         <v>40</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.477554565469992</v>
+        <v>1.47361333683283</v>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>-1</v>
       </c>
       <c r="AA147" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>-1</v>
       </c>
       <c r="AA148" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>-1</v>
       </c>
       <c r="AA149" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>-1</v>
       </c>
       <c r="AA150" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>-1</v>
       </c>
       <c r="AA151" t="n">
-        <v>6.279286738150656</v>
+        <v>6.605820722220093</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>40</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.922071825820882</v>
+        <v>1.911225540809153</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>40</v>
       </c>
       <c r="AA153" t="n">
-        <v>2.04903878032323</v>
+        <v>2.035896438083029</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>40</v>
       </c>
       <c r="AA154" t="n">
-        <v>2.032901114760624</v>
+        <v>2.019102724653187</v>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>40</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.950522736501722</v>
+        <v>1.934867026192649</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>40</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.297296083438849</v>
+        <v>1.294549624800368</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>40</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.423635425467903</v>
+        <v>1.417529054714916</v>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>40</v>
       </c>
       <c r="AA158" t="n">
-        <v>2.163188963435275</v>
+        <v>2.147991939808651</v>
       </c>
       <c r="AB158" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>40</v>
       </c>
       <c r="AA159" t="n">
-        <v>2.389070440280466</v>
+        <v>2.37193708628148</v>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>40</v>
       </c>
       <c r="AA160" t="n">
-        <v>2.498151426887392</v>
+        <v>2.479960385022996</v>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>40</v>
       </c>
       <c r="AA161" t="n">
-        <v>2.465007380031999</v>
+        <v>2.44536666460606</v>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>40</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.591560586084966</v>
+        <v>1.579361260205489</v>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>40</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.60706068487174</v>
+        <v>1.593354242402093</v>
       </c>
       <c r="AB163" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>40</v>
       </c>
       <c r="AA164" t="n">
-        <v>2.399058733589319</v>
+        <v>2.379286838001799</v>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>40</v>
       </c>
       <c r="AA165" t="n">
-        <v>2.498260729381419</v>
+        <v>2.477359322327828</v>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>40</v>
       </c>
       <c r="AA166" t="n">
-        <v>2.491098853529939</v>
+        <v>2.469425782939405</v>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>40</v>
       </c>
       <c r="AA167" t="n">
-        <v>2.390492786309661</v>
+        <v>2.367773357945795</v>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>40</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.409436823082976</v>
+        <v>1.395139183386807</v>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>40</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.265575425649657</v>
+        <v>1.255477690223567</v>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>40</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.831553327885035</v>
+        <v>1.814922198907018</v>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>40</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.88995336654542</v>
+        <v>1.872169856530406</v>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>40</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.921859898300311</v>
+        <v>1.904187110879667</v>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
@@ -16046,7 +16046,7 @@
         <v>40</v>
       </c>
       <c r="AA173" t="n">
-        <v>1.904646847349086</v>
+        <v>1.886038953133687</v>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
@@ -16136,7 +16136,7 @@
         <v>40</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.289349684207176</v>
+        <v>1.282811189678504</v>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>40</v>
       </c>
       <c r="AA175" t="n">
-        <v>1.23123529964534</v>
+        <v>1.226947323120964</v>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>40</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.780445294467111</v>
+        <v>1.767334559648429</v>
       </c>
       <c r="AB176" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>40</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.801979663643377</v>
+        <v>1.788171441035431</v>
       </c>
       <c r="AB177" t="inlineStr">
         <is>
@@ -16496,7 +16496,7 @@
         <v>40</v>
       </c>
       <c r="AA178" t="n">
-        <v>1.847673586522816</v>
+        <v>1.832646751501547</v>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
